--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 12,18</t>
+          <t>4,21; 12,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,72</t>
+          <t>4,84; 13,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,18</t>
+          <t>-3,48; 5,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,43</t>
+          <t>-1,22; 4,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 67,92</t>
+          <t>17,86; 69,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,24; 55,88</t>
+          <t>16,03; 56,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 25,78</t>
+          <t>-11,6; 24,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 61,62</t>
+          <t>-11,41; 62,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 18,44</t>
+          <t>9,39; 18,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 24,5</t>
+          <t>16,97; 24,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 15,6</t>
+          <t>7,32; 16,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 35,7</t>
+          <t>4,77; 33,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,18; 42,24</t>
+          <t>19,57; 42,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 43,51</t>
+          <t>28,28; 43,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 33,28</t>
+          <t>14,43; 34,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,02; 504,44</t>
+          <t>57,14; 537,85</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 20,44</t>
+          <t>3,05; 20,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 23,38</t>
+          <t>7,2; 23,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 23,89</t>
+          <t>6,88; 23,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,77</t>
+          <t>-0,22; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 48,51</t>
+          <t>5,58; 46,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 36,88</t>
+          <t>9,71; 36,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 46,14</t>
+          <t>11,72; 46,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 99,63</t>
+          <t>-2,95; 99,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,05</t>
+          <t>6,22; 12,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,97</t>
+          <t>9,28; 15,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,34</t>
+          <t>4,0; 10,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 24,96</t>
+          <t>3,64; 24,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 34,01</t>
+          <t>16,08; 34,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 31,52</t>
+          <t>18,11; 32,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 24,57</t>
+          <t>8,79; 24,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,13; 366,67</t>
+          <t>44,28; 340,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,45</t>
+          <t>4,21; 12,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,92</t>
+          <t>4,58; 13,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,96</t>
+          <t>-3,79; 5,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,56</t>
+          <t>-0,75; 5,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 69,23</t>
+          <t>17,64; 68,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 56,4</t>
+          <t>14,76; 54,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 24,55</t>
+          <t>-12,99; 24,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 62,58</t>
+          <t>-6,37; 72,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>176,04%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 18,2</t>
+          <t>9,43; 18,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 24,35</t>
+          <t>16,87; 24,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,0</t>
+          <t>7,7; 15,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 33,6</t>
+          <t>3,03; 6,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 42,09</t>
+          <t>19,63; 42,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,28; 43,91</t>
+          <t>27,88; 43,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 34,43</t>
+          <t>14,98; 34,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,14; 537,85</t>
+          <t>29,25; 81,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 20,27</t>
+          <t>2,86; 19,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 23,34</t>
+          <t>7,32; 23,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 23,36</t>
+          <t>6,43; 23,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,63</t>
+          <t>-0,24; 5,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 46,22</t>
+          <t>5,02; 45,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 36,94</t>
+          <t>9,89; 36,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 46,08</t>
+          <t>10,99; 47,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 99,29</t>
+          <t>-3,51; 98,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>117,96%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,09</t>
+          <t>6,13; 12,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,24</t>
+          <t>9,18; 15,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,32</t>
+          <t>4,02; 10,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 24,61</t>
+          <t>2,6; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 34,0</t>
+          <t>15,62; 34,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 32,01</t>
+          <t>17,79; 32,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 24,54</t>
+          <t>8,62; 24,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,28; 340,71</t>
+          <t>26,48; 67,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
